--- a/multiSchoolOutput/05_School_of_Physics_and_Astronomy/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/05_School_of_Physics_and_Astronomy/solution_weeks_9_10.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0112_04_4.11</t>
+          <t>0110_02_2.07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0450_03_3.32</t>
+          <t>0112_02_2.11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1043,7 +1043,7 @@
         <v>270</v>
       </c>
       <c r="F11" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1279,7 +1279,7 @@
         <v>270</v>
       </c>
       <c r="F15" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0228_-1_LG.07</t>
+          <t>0008_03_3.454</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0113_00_G.16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2119,7 +2119,7 @@
         <v>300</v>
       </c>
       <c r="F29" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0335_03_3.3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0227_00_G.06</t>
+          <t>0208_00_G.8</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0113_02_2.65</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2773,12 +2773,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2895,12 +2895,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0008_03_3.454</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0113_00_G.03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0113_01_1.9</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0422_J_J.05</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0008_03_3.454</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4071,7 +4071,7 @@
         <v>270</v>
       </c>
       <c r="F61" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4254,7 +4254,7 @@
         <v>300</v>
       </c>
       <c r="F64" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0008_03_3.454</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0228_06_6.14</t>
+          <t>0112_04_4.11</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0003_01_1.05</t>
+          <t>0112_04_4.11</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4803,7 +4803,7 @@
         <v>300</v>
       </c>
       <c r="F73" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4847,12 +4847,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0113_02_2.65</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0110_02_2.07</t>
+          <t>0283_01_1.01</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5030,12 +5030,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0113_01M_01M.27</t>
+          <t>0283_01_1.01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0113_00_G.03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0228_02_2.18</t>
+          <t>0228_06_6.14</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0208_00_G.8</t>
+          <t>0227_00_G.06</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0227_01_1.02</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0008_02_2.403</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0422_J_J.05</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6616,12 +6616,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0335_03_3.3</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6860,12 +6860,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0110_02_2.07</t>
+          <t>0228_06_6.14</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7243,7 +7243,7 @@
         <v>270</v>
       </c>
       <c r="F113" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -7287,12 +7287,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0113_00_G.03</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0113_00_G.202B</t>
+          <t>0450_01_1.62</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0113_02_2.65</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0112_02_2.11</t>
+          <t>0450_01_1.62</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0008_00_G.267</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8097,7 +8097,7 @@
         <v>300</v>
       </c>
       <c r="F127" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0112_02_2.11</t>
+          <t>0450_03_3.32</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8524,7 +8524,7 @@
         <v>270</v>
       </c>
       <c r="F134" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8690,12 +8690,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8812,12 +8812,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0112_04_4.11</t>
+          <t>0450_03_3.32</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0113_01M_01M.473</t>
+          <t>0335_00_G.13</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0311_01_1.26</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0335_03_3.3</t>
+          <t>0227_01_1.02</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0008_03_3.454</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9727,12 +9727,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9788,12 +9788,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0335_00_G.13</t>
+          <t>0226_01_1.07</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9971,12 +9971,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0226_00_GF.Z16</t>
+          <t>0113_00_G.152</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10154,12 +10154,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10171,7 +10171,7 @@
         <v>270</v>
       </c>
       <c r="F161" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0113_01M_01M.473</t>
+          <t>0335_00_G.13</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10642,12 +10642,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0113_00_G.03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10703,12 +10703,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10781,7 +10781,7 @@
         <v>300</v>
       </c>
       <c r="F171" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -10825,12 +10825,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10947,12 +10947,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -11008,12 +11008,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -11069,12 +11069,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11313,12 +11313,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0227_01_1.02</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11557,12 +11557,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">

--- a/multiSchoolOutput/05_School_of_Physics_and_Astronomy/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/05_School_of_Physics_and_Astronomy/solution_weeks_9_10.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0110_02_2.07</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0112_02_2.11</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -967,12 +967,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -984,7 +984,7 @@
         <v>120</v>
       </c>
       <c r="F10" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0113_01_1.425</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1043,7 +1043,7 @@
         <v>270</v>
       </c>
       <c r="F11" t="n">
-        <v>307</v>
+        <v>260</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0113_01_1.425</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1279,7 +1279,7 @@
         <v>270</v>
       </c>
       <c r="F15" t="n">
-        <v>307</v>
+        <v>260</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0113_00_G.152</t>
+          <t>0226_00_GF.Z16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1397,7 +1397,7 @@
         <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0335_03_3.3</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0228_-1_LG.10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1692,7 +1692,7 @@
         <v>30</v>
       </c>
       <c r="F22" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0008_03_3.454</t>
+          <t>0227_01_1.06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1858,12 +1858,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0450_01_1.55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1875,7 +1875,7 @@
         <v>45</v>
       </c>
       <c r="F25" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0113_01_1.9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2041,12 +2041,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0005_00_G.01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2058,7 +2058,7 @@
         <v>50</v>
       </c>
       <c r="F28" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0113_01_1.425</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2119,7 +2119,7 @@
         <v>300</v>
       </c>
       <c r="F29" t="n">
-        <v>307</v>
+        <v>260</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2163,12 +2163,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0226_04_4.04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2241,7 +2241,7 @@
         <v>50</v>
       </c>
       <c r="F31" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2285,12 +2285,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0226_01_1.07</t>
+          <t>0335_00_G.13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0201_04_4.12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2485,7 +2485,7 @@
         <v>30</v>
       </c>
       <c r="F35" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0208_00_G.8</t>
+          <t>0227_00_G.06</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0113_02_2.65</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2773,12 +2773,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0254_01_1.03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thursday 11:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2790,7 +2790,7 @@
         <v>15</v>
       </c>
       <c r="F40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0201_02_2.14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2851,7 +2851,7 @@
         <v>50</v>
       </c>
       <c r="F41" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0008_03_3.454</t>
+          <t>0422_J_J.03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0201_06_6.06</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2973,7 +2973,7 @@
         <v>84</v>
       </c>
       <c r="F43" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0227_02_2.54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3095,7 +3095,7 @@
         <v>15</v>
       </c>
       <c r="F45" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0335_02_2.14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3217,7 +3217,7 @@
         <v>35</v>
       </c>
       <c r="F47" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3261,12 +3261,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0201_02_2.12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3339,7 +3339,7 @@
         <v>50</v>
       </c>
       <c r="F49" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3383,12 +3383,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0450_02_2.20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3400,7 +3400,7 @@
         <v>50</v>
       </c>
       <c r="F50" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0313_00_G.10</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3705,7 +3705,7 @@
         <v>30</v>
       </c>
       <c r="F55" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0008_03_3.454</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0201_03_3.09</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3827,7 +3827,7 @@
         <v>30</v>
       </c>
       <c r="F57" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3871,12 +3871,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0313_00_G.10</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3888,7 +3888,7 @@
         <v>35</v>
       </c>
       <c r="F58" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3932,12 +3932,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0201_06_6.06</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3949,7 +3949,7 @@
         <v>100</v>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3993,12 +3993,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0113_01_1.425</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4071,7 +4071,7 @@
         <v>270</v>
       </c>
       <c r="F61" t="n">
-        <v>307</v>
+        <v>260</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0450_02_2.20</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4193,7 +4193,7 @@
         <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0113_01_1.425</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4254,7 +4254,7 @@
         <v>300</v>
       </c>
       <c r="F64" t="n">
-        <v>307</v>
+        <v>260</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4298,12 +4298,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4315,7 +4315,7 @@
         <v>80</v>
       </c>
       <c r="F65" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4359,12 +4359,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4376,7 +4376,7 @@
         <v>210</v>
       </c>
       <c r="F66" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0335_02_2.14</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4498,7 +4498,7 @@
         <v>35</v>
       </c>
       <c r="F68" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4542,12 +4542,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0209_-1_B.Z28</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0112_04_4.11</t>
+          <t>0113_01M_01M.20</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0112_04_4.11</t>
+          <t>0113_01M_01M.20</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0113_01_1.425</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4803,7 +4803,7 @@
         <v>300</v>
       </c>
       <c r="F73" t="n">
-        <v>307</v>
+        <v>260</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0210_00_G.04</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4925,7 +4925,7 @@
         <v>120</v>
       </c>
       <c r="F75" t="n">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0283_01_1.01</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5030,12 +5030,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0283_01_1.01</t>
+          <t>0113_01M_01M.20</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5108,7 +5108,7 @@
         <v>80</v>
       </c>
       <c r="F78" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0226_04_4.04</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5169,7 +5169,7 @@
         <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -5213,12 +5213,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0201_03_3.09</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5230,7 +5230,7 @@
         <v>30</v>
       </c>
       <c r="F80" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0226_00_GF.Z16</t>
+          <t>0113_00_G.152</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0450_01_1.50</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5474,7 +5474,7 @@
         <v>50</v>
       </c>
       <c r="F84" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Wednesday 11:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5657,7 +5657,7 @@
         <v>80</v>
       </c>
       <c r="F87" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5701,12 +5701,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0228_06_6.14</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0227_00_G.06</t>
+          <t>0208_00_G.8</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0201_06_6.06</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5840,7 +5840,7 @@
         <v>100</v>
       </c>
       <c r="F90" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0311_01_1.26</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0201_06_6.06</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6206,7 +6206,7 @@
         <v>100</v>
       </c>
       <c r="F96" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0450_01_1.55</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6328,7 +6328,7 @@
         <v>45</v>
       </c>
       <c r="F98" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -6372,12 +6372,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0201_04_4.12</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6389,7 +6389,7 @@
         <v>35</v>
       </c>
       <c r="F99" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0283_01_1.20</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6450,7 +6450,7 @@
         <v>45</v>
       </c>
       <c r="F100" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0227_00_G.06</t>
+          <t>0208_00_G.8</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6616,12 +6616,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0227_03_3.39</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6633,7 +6633,7 @@
         <v>15</v>
       </c>
       <c r="F103" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6677,12 +6677,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0227_00_G.06</t>
+          <t>0208_00_G.8</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0300_00_NG.02</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6816,7 +6816,7 @@
         <v>30</v>
       </c>
       <c r="F106" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0228_06_6.14</t>
+          <t>0113_01M_01M.27</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0208_00_G.8</t>
+          <t>0227_00_G.06</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0113_01_1.425</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7243,7 +7243,7 @@
         <v>270</v>
       </c>
       <c r="F113" t="n">
-        <v>307</v>
+        <v>260</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -7287,12 +7287,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0450_01_1.40</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7304,7 +7304,7 @@
         <v>50</v>
       </c>
       <c r="F114" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -7348,12 +7348,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0113_01_1.9</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0450_01_1.62</t>
+          <t>0113_01M_01M.27</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0450_03_3.35</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7548,7 +7548,7 @@
         <v>30</v>
       </c>
       <c r="F118" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -7592,12 +7592,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0228_-1_LG.10</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7609,7 +7609,7 @@
         <v>30</v>
       </c>
       <c r="F119" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -7653,12 +7653,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7670,7 +7670,7 @@
         <v>80</v>
       </c>
       <c r="F120" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Friday 17:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0450_01_1.62</t>
+          <t>0113_01M_01M.20</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0201_02_2.12</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7853,7 +7853,7 @@
         <v>50</v>
       </c>
       <c r="F123" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -7897,12 +7897,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0300_00_NG.02</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7914,7 +7914,7 @@
         <v>30</v>
       </c>
       <c r="F124" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0208_00_G.8</t>
+          <t>0227_00_G.06</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0113_01_1.425</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8097,7 +8097,7 @@
         <v>300</v>
       </c>
       <c r="F127" t="n">
-        <v>307</v>
+        <v>260</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0450_02_2.20</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8219,7 +8219,7 @@
         <v>50</v>
       </c>
       <c r="F129" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0450_03_3.32</t>
+          <t>0228_01_1.18</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0113_01_1.425</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8524,7 +8524,7 @@
         <v>270</v>
       </c>
       <c r="F134" t="n">
-        <v>307</v>
+        <v>260</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8646,7 +8646,7 @@
         <v>80</v>
       </c>
       <c r="F136" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -8690,12 +8690,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0227_01_1.02</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0201_06_6.06</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8768,7 +8768,7 @@
         <v>80</v>
       </c>
       <c r="F138" t="n">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0450_03_3.32</t>
+          <t>0228_01_1.18</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0335_00_G.13</t>
+          <t>0113_01M_01M.473</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0450_01_1.40</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9256,7 +9256,7 @@
         <v>50</v>
       </c>
       <c r="F146" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0008_03_3.454</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0422_J_J.05</t>
+          <t>0008_03_3.454</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9727,12 +9727,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0001_02_2.351</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Thursday 11:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9744,7 +9744,7 @@
         <v>15</v>
       </c>
       <c r="F154" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -9788,12 +9788,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0226_01_1.07</t>
+          <t>0113_01M_01M.473</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9910,12 +9910,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0226_00_GF.Z16</t>
+          <t>0113_00_G.152</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9971,12 +9971,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0113_00_G.152</t>
+          <t>0226_00_GF.Z16</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10154,12 +10154,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0113_01_1.425</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10171,7 +10171,7 @@
         <v>270</v>
       </c>
       <c r="F161" t="n">
-        <v>307</v>
+        <v>260</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0008_02_2.418</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10354,7 +10354,7 @@
         <v>15</v>
       </c>
       <c r="F164" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -10398,12 +10398,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0310_00_G.Z02</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0300_00_NG.01</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10598,7 +10598,7 @@
         <v>35</v>
       </c>
       <c r="F168" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -10642,12 +10642,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0201_02_2.12</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10659,7 +10659,7 @@
         <v>50</v>
       </c>
       <c r="F169" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -10703,12 +10703,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0113_01_1.425</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10781,7 +10781,7 @@
         <v>300</v>
       </c>
       <c r="F171" t="n">
-        <v>307</v>
+        <v>260</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10886,12 +10886,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0228_-1_LG.09</t>
+          <t>0001_00_G.159</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10903,7 +10903,7 @@
         <v>90</v>
       </c>
       <c r="F173" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -10947,12 +10947,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0227_01_1.06</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -11008,12 +11008,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -11069,12 +11069,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0113_02_2.65</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11313,12 +11313,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0227_01_1.02</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11374,12 +11374,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11391,7 +11391,7 @@
         <v>120</v>
       </c>
       <c r="F181" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -11435,12 +11435,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11452,7 +11452,7 @@
         <v>120</v>
       </c>
       <c r="F182" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -11496,12 +11496,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0227_00_G.02</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11513,7 +11513,7 @@
         <v>30</v>
       </c>
       <c r="F183" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -11557,12 +11557,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0254_01_1.03</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11574,7 +11574,7 @@
         <v>15</v>
       </c>
       <c r="F184" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -11618,12 +11618,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0450_01_1.50</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11635,7 +11635,7 @@
         <v>50</v>
       </c>
       <c r="F185" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
